--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU04/HRM/pre LAM_HRM-2031-0412/Panel 02/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.91421</v>
+        <v>16.93781</v>
       </c>
       <c r="D2" t="n">
-        <v>16.68456</v>
+        <v>16.40218</v>
       </c>
       <c r="E2" t="n">
-        <v>17.00002</v>
+        <v>16.76181</v>
       </c>
       <c r="F2" t="n">
-        <v>42.52745</v>
+        <v>42.7976</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05133</v>
+        <v>0.0511</v>
       </c>
       <c r="H2" t="n">
-        <v>1.82239</v>
+        <v>1.84566</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.94317</v>
+        <v>16.92622</v>
       </c>
       <c r="D3" t="n">
-        <v>16.9923</v>
+        <v>16.52778</v>
       </c>
       <c r="E3" t="n">
-        <v>17.11957</v>
+        <v>16.91399</v>
       </c>
       <c r="F3" t="n">
-        <v>43.52559</v>
+        <v>43.23705</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05055</v>
+        <v>0.05209</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85499</v>
+        <v>1.87931</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.86361</v>
+        <v>16.92452</v>
       </c>
       <c r="D4" t="n">
-        <v>17.24481</v>
+        <v>16.66737</v>
       </c>
       <c r="E4" t="n">
-        <v>16.72998</v>
+        <v>16.82077</v>
       </c>
       <c r="F4" t="n">
-        <v>43.11051</v>
+        <v>43.11999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05107</v>
+        <v>0.0514</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84801</v>
+        <v>1.83687</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.11051</v>
+        <v>17.00371</v>
       </c>
       <c r="D6" t="n">
-        <v>16.16938</v>
+        <v>15.71407</v>
       </c>
       <c r="E6" t="n">
-        <v>16.28185</v>
+        <v>16.82936</v>
       </c>
       <c r="F6" t="n">
-        <v>21.77417</v>
+        <v>21.80253</v>
       </c>
       <c r="G6" t="n">
-        <v>34.59548</v>
+        <v>34.05818</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.04088</v>
+        <v>17.06724</v>
       </c>
       <c r="D7" t="n">
-        <v>15.92457</v>
+        <v>16.32006</v>
       </c>
       <c r="E7" t="n">
-        <v>16.18919</v>
+        <v>16.91828</v>
       </c>
       <c r="F7" t="n">
-        <v>21.7573</v>
+        <v>22.07721</v>
       </c>
       <c r="G7" t="n">
-        <v>34.13835</v>
+        <v>34.69107</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.61986</v>
+        <v>16.60221</v>
       </c>
       <c r="D8" t="n">
-        <v>16.09751</v>
+        <v>16.06683</v>
       </c>
       <c r="E8" t="n">
-        <v>16.40822</v>
+        <v>16.46726</v>
       </c>
       <c r="F8" t="n">
-        <v>22.50429</v>
+        <v>22.16582</v>
       </c>
       <c r="G8" t="n">
-        <v>34.62981</v>
+        <v>34.63457</v>
       </c>
     </row>
   </sheetData>
